--- a/resultados/punto4/Bonanos2009_LMC_V_BV.xlsx
+++ b/resultados/punto4/Bonanos2009_LMC_V_BV.xlsx
@@ -139,7 +139,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>LMC massive stars (Bonanos+ 2009): V vs B-V</a:t>
+              <a:t>Estrellas masivas de la LMC (Bonanos+ 2009): V vs B−V</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -151,7 +151,7 @@
           <idx val="0"/>
           <order val="0"/>
           <tx>
-            <v>stars</v>
+            <v>estrellas</v>
           </tx>
           <spPr>
             <a:ln>
@@ -199,7 +199,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>B - V (mag)</a:t>
+                  <a:t>Índice de color B − V (mag)</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -226,7 +226,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>V (mag)</a:t>
+                  <a:t>Magnitud visual aparente V (mag)</a:t>
                 </a:r>
               </a:p>
             </rich>

--- a/resultados/punto4/Bonanos2009_LMC_V_BV.xlsx
+++ b/resultados/punto4/Bonanos2009_LMC_V_BV.xlsx
@@ -163,7 +163,13 @@
             <symbol val="circle"/>
             <size val="3"/>
             <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4FBF"/>
+              </a:solidFill>
               <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="1F4FBF"/>
+                </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -186,6 +192,8 @@
         <axId val="10"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="3"/>
+          <min val="-1"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -208,11 +216,15 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="20"/>
+        <crosses val="max"/>
+        <majorUnit val="0.5"/>
       </valAx>
       <valAx>
         <axId val="20"/>
         <scaling>
           <orientation val="maxMin"/>
+          <max val="20"/>
+          <min val="9"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -235,11 +247,9 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="min"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
